--- a/data/trans_camb/P23_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P23_R-Habitat-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,71; -2,64</t>
+          <t>-12,97; -2,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,86; -3,82</t>
+          <t>-14,07; -3,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,06; 3,98</t>
+          <t>-4,6; 4,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 6,01</t>
+          <t>-2,67; 6,54</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,45; -0,44</t>
+          <t>-7,72; -0,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,93; 0,19</t>
+          <t>-7,42; -0,02</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-26,29; -5,27</t>
+          <t>-26,9; -6,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-28,92; -8,73</t>
+          <t>-29,16; -8,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-19,89; 18,15</t>
+          <t>-18,12; 22,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-10,94; 27,41</t>
+          <t>-10,57; 30,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-20,41; -1,3</t>
+          <t>-20,82; -0,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-19,14; 0,35</t>
+          <t>-20,48; -0,13</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,25; 1,99</t>
+          <t>-6,91; 1,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,35; -4,44</t>
+          <t>-13,69; -4,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,92; 8,95</t>
+          <t>0,5; 8,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 6,75</t>
+          <t>-1,24; 6,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 4,32</t>
+          <t>-1,94; 4,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 0,0</t>
+          <t>-6,51; -0,37</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-16,12; 5,15</t>
+          <t>-15,5; 4,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-29,91; -10,77</t>
+          <t>-30,06; -11,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,38; 41,39</t>
+          <t>1,66; 40,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 31,57</t>
+          <t>-4,7; 30,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 13,74</t>
+          <t>-5,51; 14,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-17,37; 0,02</t>
+          <t>-18,38; -1,0</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 9,26</t>
+          <t>-1,14; 9,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 8,79</t>
+          <t>-1,58; 9,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 9,31</t>
+          <t>0,19; 9,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 9,06</t>
+          <t>-0,53; 8,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,67; 7,8</t>
+          <t>0,84; 7,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 7,25</t>
+          <t>0,03; 7,35</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 26,72</t>
+          <t>-2,99; 27,72</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 25,58</t>
+          <t>-4,0; 25,9</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 42,98</t>
+          <t>0,32; 40,57</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 40,36</t>
+          <t>-2,22; 38,06</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,76; 26,48</t>
+          <t>2,42; 26,83</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,34; 24,99</t>
+          <t>0,19; 24,99</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,84; 0,27</t>
+          <t>-8,86; 0,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-17,17; -8,04</t>
+          <t>-16,41; -7,84</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 2,47</t>
+          <t>-5,14; 3,01</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,54; -0,62</t>
+          <t>-9,1; -0,53</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 0,29</t>
+          <t>-5,74; 0,04</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-11,36; -5,34</t>
+          <t>-11,05; -5,3</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-19,89; 0,6</t>
+          <t>-19,75; 0,56</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-37,8; -19,2</t>
+          <t>-36,57; -19,04</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-17,06; 8,94</t>
+          <t>-16,17; 10,97</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-27,09; -2,23</t>
+          <t>-28,49; -1,89</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-15,84; 0,81</t>
+          <t>-15,52; 0,07</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-30,67; -15,65</t>
+          <t>-29,96; -15,28</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,88; -0,21</t>
+          <t>-5,37; -0,41</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-9,55; -4,83</t>
+          <t>-9,69; -4,85</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 4,18</t>
+          <t>-0,19; 4,16</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 2,69</t>
+          <t>-1,59; 2,75</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 1,26</t>
+          <t>-1,89; 1,26</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-5,1; -1,78</t>
+          <t>-4,85; -1,62</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-11,23; -0,51</t>
+          <t>-12,26; -0,99</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-21,85; -11,62</t>
+          <t>-22,03; -11,57</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 17,14</t>
+          <t>-0,77; 17,04</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-5,71; 10,86</t>
+          <t>-5,86; 11,33</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-6,15; 3,84</t>
+          <t>-5,48; 3,81</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-14,66; -5,37</t>
+          <t>-14,05; -4,95</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P23_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P23_R-Habitat-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,97; -2,77</t>
+          <t>-12,83; -2,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,07; -3,72</t>
+          <t>-14,01; -3,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 4,82</t>
+          <t>-4,9; 4,75</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 6,54</t>
+          <t>-2,58; 7,03</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,72; -0,38</t>
+          <t>-7,48; -0,3</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,42; -0,02</t>
+          <t>-7,07; 0,25</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-26,9; -6,1</t>
+          <t>-26,44; -4,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-29,16; -8,47</t>
+          <t>-29,09; -8,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-18,12; 22,55</t>
+          <t>-19,37; 22,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-10,57; 30,5</t>
+          <t>-10,37; 32,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-20,82; -0,97</t>
+          <t>-20,5; -1,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-20,48; -0,13</t>
+          <t>-18,95; 1,31</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,91; 1,84</t>
+          <t>-7,04; 1,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,69; -4,68</t>
+          <t>-13,75; -4,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,5; 8,88</t>
+          <t>0,6; 8,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 6,52</t>
+          <t>-1,37; 6,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 4,53</t>
+          <t>-1,85; 4,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,51; -0,37</t>
+          <t>-6,29; -0,44</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-15,5; 4,62</t>
+          <t>-15,94; 5,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-30,06; -11,52</t>
+          <t>-30,22; -11,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,66; 40,64</t>
+          <t>1,64; 40,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 30,48</t>
+          <t>-5,2; 30,71</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 14,54</t>
+          <t>-5,36; 13,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-18,38; -1,0</t>
+          <t>-17,91; -1,22</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 9,59</t>
+          <t>-1,53; 9,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 9,04</t>
+          <t>-2,22; 9,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 9,25</t>
+          <t>0,43; 9,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 8,83</t>
+          <t>-0,58; 8,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,84; 7,85</t>
+          <t>0,93; 8,12</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,03; 7,35</t>
+          <t>0,54; 7,22</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 27,72</t>
+          <t>-3,74; 26,82</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 25,9</t>
+          <t>-5,53; 26,74</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,32; 40,57</t>
+          <t>1,08; 42,17</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 38,06</t>
+          <t>-2,06; 38,64</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,42; 26,83</t>
+          <t>3,01; 28,02</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,19; 24,99</t>
+          <t>1,47; 24,66</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,86; 0,25</t>
+          <t>-9,14; 0,24</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-16,41; -7,84</t>
+          <t>-16,49; -7,8</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 3,01</t>
+          <t>-5,72; 2,39</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-9,1; -0,53</t>
+          <t>-8,89; -0,99</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,74; 0,04</t>
+          <t>-5,68; 0,11</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-11,05; -5,3</t>
+          <t>-11,11; -5,27</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-19,75; 0,56</t>
+          <t>-20,06; 0,56</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-36,57; -19,04</t>
+          <t>-36,81; -19,22</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-16,17; 10,97</t>
+          <t>-17,81; 8,5</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-28,49; -1,89</t>
+          <t>-28,27; -3,59</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-15,52; 0,07</t>
+          <t>-15,47; 0,17</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-29,96; -15,28</t>
+          <t>-30,06; -15,32</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,37; -0,41</t>
+          <t>-5,41; -0,63</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-9,69; -4,85</t>
+          <t>-9,64; -4,95</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 4,16</t>
+          <t>-0,55; 3,97</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 2,75</t>
+          <t>-1,48; 2,78</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 1,26</t>
+          <t>-2,02; 1,27</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,85; -1,62</t>
+          <t>-4,98; -1,66</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-12,26; -0,99</t>
+          <t>-12,23; -1,45</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-22,03; -11,57</t>
+          <t>-22,01; -11,82</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 17,04</t>
+          <t>-1,97; 16,35</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 11,33</t>
+          <t>-5,61; 11,17</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 3,81</t>
+          <t>-5,87; 3,89</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-14,05; -4,95</t>
+          <t>-14,51; -4,96</t>
         </is>
       </c>
     </row>
